--- a/e2e/expectedData/sub_Report_KKP_-_Benefit_others.xlsx
+++ b/e2e/expectedData/sub_Report_KKP_-_Benefit_others.xlsx
@@ -47,6 +47,18 @@
     <t>TOTAL (USD)</t>
   </si>
   <si>
+    <t>RIMBUN SIBURIAN</t>
+  </si>
+  <si>
+    <t>Quality Assuance Senior Engineer</t>
+  </si>
+  <si>
+    <t>Catatan January rimbun siburian</t>
+  </si>
+  <si>
+    <t>$ 262.50</t>
+  </si>
+  <si>
     <t>CELIA MARIA REGO DE FATIMA</t>
   </si>
   <si>
@@ -59,25 +71,13 @@
     <t>$ 85.00</t>
   </si>
   <si>
-    <t>RIMBUN SIBURIAN</t>
-  </si>
-  <si>
-    <t>Quality Assuance Senior Engineer</t>
-  </si>
-  <si>
-    <t>Catatan January rimbun siburian</t>
-  </si>
-  <si>
-    <t>$ 262.50</t>
-  </si>
-  <si>
     <t>TOTAL</t>
   </si>
   <si>
     <t>$ 347.50</t>
   </si>
   <si>
-    <t>DILI, 26 Agustus 2026</t>
+    <t>DILI, 09 September 2026</t>
   </si>
   <si>
     <t>NIK.</t>
@@ -513,7 +513,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="2">
-        <v>92003</v>
+        <v>81010</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>10</v>
@@ -522,7 +522,7 @@
         <v>11</v>
       </c>
       <c r="E5" s="2">
-        <v>340.0</v>
+        <v>1050.0</v>
       </c>
       <c r="F5" s="2">
         <v>0.25</v>
@@ -539,7 +539,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2">
-        <v>81010</v>
+        <v>92003</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>14</v>
@@ -548,7 +548,7 @@
         <v>15</v>
       </c>
       <c r="E6" s="2">
-        <v>1050.0</v>
+        <v>340.0</v>
       </c>
       <c r="F6" s="2">
         <v>0.25</v>

--- a/e2e/expectedData/sub_Report_KKP_-_Benefit_others.xlsx
+++ b/e2e/expectedData/sub_Report_KKP_-_Benefit_others.xlsx
@@ -77,7 +77,7 @@
     <t>$ 347.50</t>
   </si>
   <si>
-    <t>DILI, 09 September 2026</t>
+    <t>DILI, 10 September 2026</t>
   </si>
   <si>
     <t>NIK.</t>
